--- a/Result/checksun_type/農業科技業.xlsx
+++ b/Result/checksun_type/農業科技業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>42.72</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>43.99</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>45.31</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>45.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>364852.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>477204.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>477204.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>967501.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1359132.82</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1359132.82</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-187245.2591256917</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>364852</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>364852.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>42.66</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>44.1</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>45.41</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>45.41</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>662825.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1123615.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1123615.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>994102.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1371004.56</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1371004.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-162439.6643895779</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>662825</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>662825.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>42.93</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>44.23</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>417524.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1361782.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1361782</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1005082.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1368735.7</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1368735.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-153127.3624669304</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>417524</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>417524.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>43.15</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>44.37</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>45.6</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>525461.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1429682.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>1429682</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1225882.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1377225.96</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1377225.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-108072.9896321862</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>525461</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>525461.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>43.44</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>44.51</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>45.7</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>45.7</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>415360.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1432073.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1432073.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1178479.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1382024.44</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1382024.44</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-51414.5288099735</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>415360</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>415360.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>43.88</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>44.86</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>45.8</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3596909.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1457799.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1457799.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1209837.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1385213.8</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1385213.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>43158.89839354344</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3596909</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3596909.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>44.35</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>44.98</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>45.9</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>45.9</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1853656.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>864589.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>864589.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>893206.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1329456.22</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1329456.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-164157.8448297731</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1853656</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1853656.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>44.52999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>45.04</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>45.97</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>45.97</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>757024.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>648383.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>648383.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>766264.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1335849.1</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1335849.1</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-267684.733547733</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>757024</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>757024.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>44.6</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>45.09</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>46.03</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>46.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>537420.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1022083.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1022083.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>802796.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1332581.48</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1332581.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-288523.8340895427</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>537420</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>537420.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>44.6</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>46.09</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>46.09</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>543987.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>924884.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>924884.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>822217.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1336983.2</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1336983.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-284460.5550746443</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>543987</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>543987.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>44.59</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>45.18</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>46.15</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>46.15</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>630861.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>961875.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>961875.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>857005.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1333774.9</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1333774.9</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-269200.1723721232</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>630861</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>630861.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>34.23999999999999</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>34.62</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>35.12</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>35.12</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>975767.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1900636.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1900636.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>2171045.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>6378257.22</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>6378257.22</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1379162.686209632</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>975767</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>975767.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>34.21</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>34.65</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>35.13</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>35.13</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>941745.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>2056334.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>2056334.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2310710.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>6389216.66</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>6389216.66</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1427379.006908488</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>941745</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>941745.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>34.18</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>34.71</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>35.16</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>35.16</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2024098.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>2766313.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>2766313.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2702312.7</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>6430744.36</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>6430744.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-1441636.429088694</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2024098</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2024098.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>34.25</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>34.9</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>35.19</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>35.19</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>2328344.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>2881727.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>2881727.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2895235.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>6439693.4</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>6439693.4</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-1526483.552592963</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>2328344</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2328344.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>34.37</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>35.3</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>35.22</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>35.22</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>3233227.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>2886957.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>2886957</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>2879802.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>6417177.4</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>6417177.4</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-1625774.245006455</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>3233227</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>3233227.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>34.48999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>35.49</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>35.26</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>1754260.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>2441455.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>2441455.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>2754500.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>6374538.34</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>6374538.34</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-1806506.475418357</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>1754260</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1754260.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>34.58</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>35.52</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>35.29</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>35.29</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>4491637.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>2565086.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>2565086.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>3017552.8</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>6355876.38</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>6355876.38</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-1841716.53759899</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>4491637</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>4491637.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>34.64999999999999</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>35.33</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>35.33</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>2601169.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>2638312.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>2638312.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>3241809.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>6291832.52</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>6291832.52</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-2119531.428657074</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>2601169</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2601169.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>34.68</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>35.57</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>35.36</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>35.36</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>2354492.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2908743.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>2908743.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>3592555.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>6288296.28</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>6288296.28</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-2238162.150573726</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>2354492</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2354492.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>34.68</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>35.57</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>35.38</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>35.38</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1005720.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2872648.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2872648.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>3868233.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>6290507.12</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>6290507.12</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-2301270.569362739</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1005720</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1005720.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>34.7</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>35.57</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>35.4</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>35.4</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>2372413.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>3067544.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>3067544.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>4340574.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>6350943.74</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>6350943.74</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-2164725.93301266</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>2372413</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>2372413.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>50.96</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>51.47</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>52.21</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>51.47</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>52.21</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>17956885.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>8950584.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>8950584.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>8157639.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>6929587.06</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>6929587.06</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>693693.9518489158</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>17956885</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>17956885.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>50.48999999999999</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>51.48</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>52.22</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>52.22</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>4197152.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>6275232.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>6275232.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>6626872.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>7203813.28</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>7203813.28</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-200974.9605394397</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>4197152</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>4197152.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>50.38</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>51.58</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>52.31</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>52.31</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>5019179.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>6863569.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>6863569</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>6542082.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>7419548.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>7419548</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>2361.377496462315</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>5019179</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>5019179.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>50.5</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>51.71</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>52.41</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>52.41</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>8332853.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>7339532.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>7339532.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>6379937.7</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>7459733.34</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>7459733.34</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>204683.2040657345</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>8332853</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>8332853.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>50.68</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>51.8</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>52.5</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>9246853.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>6599368.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>6599368.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>7443375.8</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>7455734.22</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>7455734.22</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>131367.7704480607</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>9246853</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>9246853.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>50.86</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>51.85</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>52.58</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>52.58</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>4580125.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>7364694.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>7364694</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>7932550.0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>7814412.12</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>7814412.12</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-75988.84080747515</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>4580125</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>4580125.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>51.27</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>51.96</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>52.72</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>52.72</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>7138835.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>6978512.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>6978512.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>8486901.6</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>7857936.62</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>7857936.62</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>130507.8874277407</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>7138835</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>7138835.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>51.64</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>52.07</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>52.85</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>52.85</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>7398995.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>6220595.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>6220595.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>8095639.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>7785881.66</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>7785881.66</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>146694.7174984878</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>7398995</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>7398995.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>51.84</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>52.13</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>52.96</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>52.96</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>4632033.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>5420343.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>5420343.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>7767470.7</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>7803894.44</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>7803894.44</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>136705.377688894</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>4632033</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>4632033.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>51.82000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>52.17</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>53.05</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>53.05</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>13073482.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>8287383.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>8287383.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>7521303.8</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>7869389.7</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>7869389.7</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>414012.7716148719</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>13073482</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>13073482.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>52.17</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>53.14</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>53.14</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>2649218.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>8500406.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>8500406</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>6617376.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>7740105.52</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>7740105.52</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-109060.9431914054</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>2649218</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>2649218.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>23.62</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>24.01</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>24.32</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>352.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>1242.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>1242.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1186.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>1036.92</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>1036.92</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-14.4107574645036</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>352</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>352.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>23.6</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>24.33</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>24.33</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1197.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1512.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1512.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>1221.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>1171.82</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>1171.82</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>57.71011528706072</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1197</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1197.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>23.64</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>24.12</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>24.36</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>24.36</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>492.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1485.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1485</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>1183.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>1160.4</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>1160.4</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>68.14314367190059</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>492</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>492.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>23.72</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>24.19</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>24.4</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>1452.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1517.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1517.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>1182.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>1169.96</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>1169.96</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>156.1495005191039</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>1452</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>1452.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>23.79</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>24.28</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>24.44</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>24.44</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>2720.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1440.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1440</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1219.4</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>1144.44</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>1144.44</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>173.4389567108549</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>2720</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>2720.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>23.88</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>24.47</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>24.47</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1700.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1129.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1129.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>996.7</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>1096.88</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>1096.88</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>56.08678853082563</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1700</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>23.89</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>24.34</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>24.5</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>24.5</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>1061.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>929.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>929.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>911.1</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>1083.12</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>1083.12</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-4.276551316745554</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>1061</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>1061.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>23.9</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>24.36</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>24.53</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>24.53</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>654.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>882.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>882</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>835.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>1093.62</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>1093.62</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-21.89287426624901</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>654</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>654.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>23.91</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>24.38</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>24.56</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>24.56</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>1065.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>847.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>847.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>807.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>1097.52</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>1097.52</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-2.670018684602155</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>1065</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1065.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>23.94</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>24.6</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1168.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>998.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>998.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>742.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>1095.28</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>1095.28</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-19.14915290065665</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1168</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1168.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>23.97</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>24.63</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>24.63</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>701.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>863.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>863.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>670.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>1088.46</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>1088.46</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-53.04258917713958</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>701</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>701.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>63.82</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>54.14</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>63.82</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>54.14</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>16001469.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>19996474.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>19996474.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>55086319.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>25070064.28</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>25070064.28</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-3944310.55324452</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>16001469</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>16001469.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>53.8</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>64.56</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>53.73</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>53.73</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>13807588.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>23777429.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>23777429.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>54425533.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>24750839.9</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>24750839.9</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-2733457.873315699</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>13807588</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>13807588.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>54.14000000000001</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>65.8</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>53.42</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>53.42</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>32443436.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>31680134.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>31680134.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>54178663.7</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>24499720.74</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>24499720.74</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-670986.1565132588</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>32443436</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>32443436.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>56.73999999999999</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>67.1</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>53.21</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>53.21</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>13607992.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>43824688.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>43824688.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>52778418.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>23864128.78</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>23864128.78</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>302667.8016514182</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>13607992</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>13607992.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>67.96</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>52.97</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>67.95999999999999</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>52.97</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>24121887.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>84772306.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>84772306.59999999</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>51955402.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>23598443.82</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>23598443.82</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>3700875.748970546</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>24121887</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>24121887.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>63.14</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>68.39</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>52.69</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>68.39</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>52.69</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>34906243.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>90176165.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>90176165.40000001</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>51086664.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>23117663.44</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>23117663.44</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>7296795.646963216</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>34906243</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>34906243.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>64.60000000000001</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>52.4</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>53321114.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>85073637.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>85073637.59999999</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>49187526.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>22420646.66</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>22420646.66</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>11017757.51384691</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>53321114</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>53321114.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>65.96000000000001</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>68.44</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>52.04</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>68.44</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>52.04</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>93166208.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>76677193.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>76677193</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>45691253.3</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>21358539.98</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>21358539.98</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>13966904.09104338</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>93166208</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>93166208.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>65.94</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>67.71</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>51.55</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>67.70999999999999</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>51.55</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>218346081.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>61732148.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>61732148</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>37735256.3</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>19506206.82</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>19506206.82</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>13412035.41235821</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>218346081</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>218346081.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>65.78</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>66.41</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>50.93</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>66.41</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>50.93</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>51141181.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>19138497.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>19138497.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>18083906.8</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>15141675.98</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>15141675.98</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-1271764.643347684</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>51141181</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>51141181.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>66.4</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>65.01</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>50.36</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>50.36</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>9393604.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>11997164.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>11997164.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>15519974.6</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>14120970.28</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>14120970.28</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-4288390.985665116</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>9393604</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>9393604.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>19.34</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>21.16</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>19.62</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>846.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>966.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>966.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>2408.5</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>4985.9</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>4985.9</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-1395.392889782681</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>846</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>846.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>19.29</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>21.51</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>19.62</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>515.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1248.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1248</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>2596.3</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>4981.68</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>4981.68</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-1462.288547516903</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>515</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>515.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>19.35</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>21.8</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>19.62</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>960.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1754.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1754.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>2828.3</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>4984.7</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>4984.7</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-1470.164896154473</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>960</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>960.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>19.38</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>21.97</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>19.62</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1084.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>2139.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>2139</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>2997.0</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>4982.1</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>4982.1</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-1476.589505059771</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1084</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1084.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>19.55</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>22.04</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>19.62</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>1428.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>3192.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>3192.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>3243.6</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>4972.5</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>4972.5</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-1446.31789260092</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>1428</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1428.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>19.87</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>22.02</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>19.63</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>2253.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>3850.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>3850.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>3671.3</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>4958.62</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>4958.62</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-1388.275664352529</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>2253</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>2253.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>20.47</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>21.91</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>19.63</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>3046.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>3944.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>3944.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>3862.0</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>4927.7</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>4927.7</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-1344.169778842237</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>3046</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>3046.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>20.96</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>19.62</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>2884.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>3902.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>3902.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>4376.2</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>4887.16</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>4887.16</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-1318.119593154597</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>2884</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>2884.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>21.35</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>19.62</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>6350.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>3855.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>3855</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>4636.4</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>4844.16</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>4844.16</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-1216.47219955959</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>6350</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>6350.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>21.71</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>21.52</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>19.61</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>19.61</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>4719.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>3295.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>3295</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>5159.9</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>4723.96</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>4723.96</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-1399.173344439594</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>4719</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>4719.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>21.82</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>21.32</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>2724.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>3492.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>3492.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>7435.0</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>4648.16</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>4648.16</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-1435.454503395329</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>2724</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>2724.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29647,11 +29251,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
           <t>2459</t>
@@ -29833,41 +29433,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO68" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT68" t="inlineStr">
         <is>
           <t>0</t>
@@ -29888,20 +29484,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>0</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>0</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29510,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>0</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29679,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29863,11 @@
           <t>57.72000000000001</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>57.76</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>57.76</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29914,16 @@
           <t>880.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>956.2</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>956.2</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>1068.3</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>2867.84</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>2867.84</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29940,10 @@
           <t>-478.7818186679726</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>880</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>880.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30109,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30293,11 @@
           <t>57.58000000000001</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>57.79</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>57.79</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30344,16 @@
           <t>521.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>913.8</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>913.8</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>1011.7</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>2881.34</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>2881.34</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30370,10 @@
           <t>-519.2002646672681</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>521</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>521.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30539,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30723,11 @@
           <t>57.58000000000001</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>57.83</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>57.83</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30774,16 @@
           <t>1265.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>1137.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>1137.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>1361.2</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>2907.14</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>2907.14</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30800,10 @@
           <t>-519.9337494995739</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1265</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1265.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30969,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31153,11 @@
           <t>57.73999999999999</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>57.88</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>57.88</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31204,16 @@
           <t>1627.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>1193.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>1193.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>1402.2</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>2895.68</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>2895.68</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31230,10 @@
           <t>-582.1268082064539</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>1627</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>1627.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31399,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31583,11 @@
           <t>57.92</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>57.71</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>57.94</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>57.94</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31634,16 @@
           <t>488.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>1166.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>1166.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>1315.3</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>2869.42</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>2869.42</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31660,10 @@
           <t>-688.9695060660524</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>488</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>488.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31829,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32013,11 @@
           <t>57.88</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>57.95</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>57.99</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>57.99</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32064,16 @@
           <t>668.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>1180.4</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>1180.4</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>1302.1</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>2875.28</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>2875.28</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32090,10 @@
           <t>-694.9601635059767</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>668</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32259,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32443,11 @@
           <t>57.84</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>57.9</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>58.04</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>58.04</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32494,16 @@
           <t>1641.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>1109.6</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>1109.6</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>1270.4</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>2873.08</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>2873.08</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32520,10 @@
           <t>-697.9839540092264</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>1641</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>1641.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32689,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32873,11 @@
           <t>57.7</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>57.87</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>58.09</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>58.09</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32924,16 @@
           <t>1543.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>1584.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>1584.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>1215.5</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>2860.68</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>2860.68</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32950,10 @@
           <t>-781.6256563706825</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>1543</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>1543.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33119,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33303,11 @@
           <t>57.4</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>57.85</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>58.14</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>58.14</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33354,16 @@
           <t>1494.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>1611.0</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>1611</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>1163.3</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>2836.3</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>2836.3</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33380,10 @@
           <t>-862.6986005880954</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>1494</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>1494.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33549,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33733,11 @@
           <t>57.3</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>58.19</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>58.19</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33784,16 @@
           <t>556.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>1463.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>1463.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>1097.9</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>2828.08</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>2828.08</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33810,10 @@
           <t>-942.4564280205386</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>556</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>556.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33979,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34163,11 @@
           <t>57.32000000000001</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>57.76</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>58.25</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>58.25</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34214,16 @@
           <t>314.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>1423.8</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>1423.8</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>1166.4</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>2838.32</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>2838.32</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34240,10 @@
           <t>-922.2370233518673</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>314</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>314.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
